--- a/stories/arbres/TREE-SAN-006.xlsx
+++ b/stories/arbres/TREE-SAN-006.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Zoé va au marché avec papa. Maman les rejoint. Le nez de Zoé chatouille. Atchoum, tout doux. Papa dit : on prend un mouchoir. Puis on le met à la poubelle.</t>
+          <t>Zoé va au marché avec papa. Maman les rejoint. Le nez de Zoé chatouille. Atchoum, tout doux. On prend un mouchoir. Puis on le met à la poubelle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé va au marché avec papa. Maman les rejoint. Le nez de Zoé chatouille. Atchoum, tout doux.
+papa|On prend un mouchoir.
+narrateur|Puis on le met à la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1519,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1519,7 +1548,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom est près de l'étal des fruits. Zoé a le nez plein. Papa tend un mouchoir. Zoé prend le mouchoir. Elle se mouche. Puis elle va à la poubelle. Elle jette le mouchoir. Tom dit : bien.</t>
+          <t>Tom est près de l'étal des fruits. Zoé a le nez plein. Papa tend un mouchoir. Zoé prend le mouchoir. Elle se mouche. Puis elle va à la poubelle. Elle jette le mouchoir. Bien.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1657,6 +1686,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom est près de l'étal des fruits. Zoé a le nez plein. Papa tend un mouchoir. Zoé prend le mouchoir. Elle se mouche. Puis elle va à la poubelle. Elle jette le mouchoir.
+enfant-m|Bien.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1868,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé se mouche. Que prend-elle ?</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2041,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a le nez plus libre. Le mouchoir est à la poubelle. Tom est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2193,6 +2238,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
     </row>
@@ -2357,6 +2407,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Au stand des jouets, il y a des cubes. Zoé a déjà pris un mouchoir. Elle l'a jeté à la poubelle. Elle peut empiler. Tom l'aide.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2547,6 +2602,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2709,6 +2769,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Papa achète une pomme. Zoé a le mouchoir à la poubelle. Son nez respire. Tom tient le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2871,6 +2936,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3033,6 +3103,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Maman prend un yaourt. Zoé a jeté le mouchoir à la poubelle. Tom sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3195,6 +3270,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3357,6 +3437,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Le pain est chaud. Zoé a pris un mouchoir. Puis la poubelle. Tom dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3519,6 +3604,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3681,6 +3771,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Tom montre un petit livre d'images. Zoé a le nez propre. Mouchoir, puis poubelle. Elle tourne une page. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3871,6 +3966,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4033,6 +4133,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Une pomme rouge. Zoé a mis le mouchoir à la poubelle. Tom ferme le livre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4195,6 +4300,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4357,6 +4467,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Un yaourt frais. Zoé a pris un mouchoir. Poubelle. Tom range.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4519,6 +4634,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4681,6 +4801,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Un morceau de pain. Zoé a le nez libre. Mouchoir à la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4843,6 +4968,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4867,7 +4997,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Il y a une petite dînette en bois. Tom s'assoit. Zoé a déjà jeté le mouchoir à la poubelle. Elle joue un peu. Maman dit : nez propre.</t>
+          <t>Il y a une petite dînette en bois. Tom s'assoit. Zoé a déjà jeté le mouchoir à la poubelle. Elle joue un peu. Nez propre.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5005,6 +5135,12 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Il y a une petite dînette en bois. Tom s'assoit. Zoé a déjà jeté le mouchoir à la poubelle. Elle joue un peu.
+maman|Nez propre.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5195,6 +5331,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5357,6 +5498,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Papa montre une pomme. Zoé a le mouchoir à la poubelle. Tom pose une assiette.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5519,6 +5665,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5681,6 +5832,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Maman a un yaourt. Zoé a pris un mouchoir. Puis la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5843,6 +5999,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5867,7 +6028,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Le pain craque. Zoé a jeté le mouchoir. Poubelle. Tom dit : on rentre.</t>
+          <t>Le pain craque. Zoé a jeté le mouchoir. Poubelle. On rentre.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6005,6 +6166,12 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Le pain craque. Zoé a jeté le mouchoir. Poubelle.
+enfant-m|On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6167,6 +6334,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6191,7 +6363,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Léa est près des fleurs. Zoé sent un chatouillement. Maman sort un mouchoir. Zoé prend le mouchoir. Elle se mouche. Elle trouve la poubelle. Elle jette. Léa dit : ton nez respire.</t>
+          <t>Léa est près des fleurs. Zoé sent un chatouillement. Maman sort un mouchoir. Zoé prend le mouchoir. Elle se mouche. Elle trouve la poubelle. Elle jette. Ton nez respire.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6329,6 +6501,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Léa est près des fleurs. Zoé sent un chatouillement. Maman sort un mouchoir. Zoé prend le mouchoir. Elle se mouche. Elle trouve la poubelle. Elle jette.
+enfant-f|Ton nez respire.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6505,6 +6683,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a pris quoi, près des fleurs ?</t>
         </is>
       </c>
     </row>
@@ -6673,6 +6856,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Les fleurs sentent bon. Zoé aussi respire. Le mouchoir est à la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6865,6 +7053,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
     </row>
@@ -7029,6 +7222,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Léa empile des cubes. Zoé a le nez propre. Mouchoir, poubelle. Elle pose un cube bleu.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7219,6 +7417,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7381,6 +7584,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Une pomme dans le sac. Zoé a jeté le mouchoir à la poubelle. Léa applaudit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7543,6 +7751,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7705,6 +7918,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Un yaourt. Zoé a pris un mouchoir. Poubelle. Léa tient la main.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7867,6 +8085,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7891,7 +8114,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Du pain chaud. Zoé a le mouchoir à la poubelle. Léa dit : on y va.</t>
+          <t>Du pain chaud. Zoé a le mouchoir à la poubelle. On y va.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8029,6 +8252,12 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Du pain chaud. Zoé a le mouchoir à la poubelle.
+enfant-f|On y va.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8191,6 +8420,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8353,6 +8587,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa ouvre un livre d'images. Zoé a déjà mis le mouchoir à la poubelle. Elle écoute. Papa tourne la page.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8543,6 +8782,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8705,6 +8949,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Papa prend une pomme. Zoé a le mouchoir à la poubelle. Léa ferme le livre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8867,6 +9116,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9029,6 +9283,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Maman prend un yaourt. Zoé a pris un mouchoir. Puis la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9191,6 +9450,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9353,6 +9617,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Le pain est dans le filet. Zoé a jeté le mouchoir. Poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9515,6 +9784,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9539,7 +9813,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Une dînette miniature. Léa sert du thé imaginaire. Zoé a le nez libre. Mouchoir à la poubelle. Elle dit : à table.</t>
+          <t>Une dînette miniature. Léa sert du thé imaginaire. Zoé a le nez libre. Mouchoir à la poubelle. À table.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9677,6 +9951,12 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Une dînette miniature. Léa sert du thé imaginaire. Zoé a le nez libre. Mouchoir à la poubelle.
+narrateur|À table.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9867,6 +10147,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10029,6 +10314,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Une vraie pomme. Zoé a mis le mouchoir à la poubelle. Léa range.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10191,6 +10481,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10353,6 +10648,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Un vrai yaourt. Zoé a pris un mouchoir. Poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10515,6 +10815,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10677,6 +10982,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Un vrai morceau de pain. Zoé a le mouchoir à la poubelle. Léa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10839,6 +11149,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10863,7 +11178,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sami est près du stand de pain. Zoé a le nez qui coule. Papa dit : mouchoir. Zoé prend un mouchoir. Elle se mouche. Sami montre la poubelle. Zoé jette. Son nez est plus libre.</t>
+          <t>Sami est près du stand de pain. Zoé a le nez qui coule. Mouchoir. Zoé prend un mouchoir. Elle se mouche. Sami montre la poubelle. Zoé jette. Son nez est plus libre.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11001,6 +11316,13 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sami est près du stand de pain. Zoé a le nez qui coule.
+papa|Mouchoir.
+narrateur|Zoé prend un mouchoir. Elle se mouche. Sami montre la poubelle. Zoé jette. Son nez est plus libre.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11181,6 +11503,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Sami montre la poubelle. Zoé a pris quoi avant ?</t>
         </is>
       </c>
     </row>
@@ -11349,6 +11676,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Le pain sent bon. Zoé respire mieux. Le mouchoir est à la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11541,6 +11873,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
     </row>
@@ -11705,6 +12042,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sami construit. Zoé a déjà jeté le mouchoir à la poubelle. Elle pose un cube. Papa surveille.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11895,6 +12237,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12057,6 +12404,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Une pomme pour plus tard. Zoé a le mouchoir à la poubelle. Sami range les cubes.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12219,6 +12571,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12243,7 +12600,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Un yaourt. Zoé a pris un mouchoir. Poubelle. Sami dit : on rentre.</t>
+          <t>Un yaourt. Zoé a pris un mouchoir. Poubelle. On rentre.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12381,6 +12738,12 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Un yaourt. Zoé a pris un mouchoir. Poubelle.
+enfant-m|On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12543,6 +12906,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12705,6 +13073,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Le pain de Sami. Zoé a jeté le mouchoir à la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12867,6 +13240,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12891,7 +13269,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Sami a un petit livre. Zoé écoute, nez propre. Mouchoir, puis poubelle. Maman dit : bien.</t>
+          <t>Sami a un petit livre. Zoé écoute, nez propre. Mouchoir, puis poubelle. Bien.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13029,6 +13407,12 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a un petit livre. Zoé écoute, nez propre. Mouchoir, puis poubelle.
+maman|Bien.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13219,6 +13603,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13381,6 +13770,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Papa choisit une pomme. Zoé a le mouchoir à la poubelle. Sami ferme le livre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13543,6 +13937,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13705,6 +14104,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Maman choisit un yaourt. Zoé a pris un mouchoir. Poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13867,6 +14271,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14029,6 +14438,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sami sent le pain. Zoé a jeté le mouchoir. Poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14191,6 +14605,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14353,6 +14772,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sami fait la dînette. Zoé a le nez libre. Le mouchoir est déjà à la poubelle. Elle sert une tasse imaginaire.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14543,6 +14967,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14705,6 +15134,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Une pomme vraie. Zoé a mis le mouchoir à la poubelle. Sami range.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14867,6 +15301,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15029,6 +15468,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Un yaourt vrai. Zoé a pris un mouchoir. Puis la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15191,6 +15635,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15215,7 +15664,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Un morceau de pain vrai. Zoé a le mouchoir à la poubelle. Sami dit : au revoir marché.</t>
+          <t>Un morceau de pain vrai. Zoé a le mouchoir à la poubelle. Au revoir marché.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15353,6 +15802,12 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Un morceau de pain vrai. Zoé a le mouchoir à la poubelle.
+enfant-m|Au revoir marché.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15515,6 +15970,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15533,7 +15993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15571,6 +16031,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-006.xlsx
+++ b/stories/arbres/TREE-SAN-006.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Puis on le met à la poubelle.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1524,6 +1530,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1692,6 +1699,7 @@
 enfant-m|Bien.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1875,6 +1883,7 @@
           <t>narrateur|Zoé se mouche. Que prend-elle ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2046,6 +2055,7 @@
           <t>narrateur|Zoé a le nez plus libre. Le mouchoir est à la poubelle. Tom est encore là.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2245,6 +2255,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2412,6 +2423,7 @@
           <t>narrateur|Au stand des jouets, il y a des cubes. Zoé a déjà pris un mouchoir. Elle l'a jeté à la poubelle. Elle peut empiler. Tom l'aide.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2607,6 +2619,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2774,6 +2787,7 @@
           <t>narrateur|Papa achète une pomme. Zoé a le mouchoir à la poubelle. Son nez respire. Tom tient le sac.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2941,6 +2955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3108,6 +3123,7 @@
           <t>narrateur|Maman prend un yaourt. Zoé a jeté le mouchoir à la poubelle. Tom sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3275,6 +3291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3442,6 +3459,7 @@
           <t>narrateur|Le pain est chaud. Zoé a pris un mouchoir. Puis la poubelle. Tom dit merci.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3609,6 +3627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3776,6 +3795,7 @@
           <t>narrateur|Tom montre un petit livre d'images. Zoé a le nez propre. Mouchoir, puis poubelle. Elle tourne une page. Papa est là.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3971,6 +3991,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4138,6 +4159,7 @@
           <t>narrateur|Une pomme rouge. Zoé a mis le mouchoir à la poubelle. Tom ferme le livre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4305,6 +4327,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4472,6 +4495,7 @@
           <t>narrateur|Un yaourt frais. Zoé a pris un mouchoir. Poubelle. Tom range.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4639,6 +4663,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4806,6 +4831,7 @@
           <t>narrateur|Un morceau de pain. Zoé a le nez libre. Mouchoir à la poubelle.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4973,6 +4999,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5141,6 +5168,7 @@
 maman|Nez propre.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5336,6 +5364,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5503,6 +5532,7 @@
           <t>narrateur|Papa montre une pomme. Zoé a le mouchoir à la poubelle. Tom pose une assiette.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5670,6 +5700,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5837,6 +5868,7 @@
           <t>narrateur|Maman a un yaourt. Zoé a pris un mouchoir. Puis la poubelle.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6004,6 +6036,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6172,6 +6205,7 @@
 enfant-m|On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6339,6 +6373,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6507,6 +6542,7 @@
 enfant-f|Ton nez respire.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6690,6 +6726,7 @@
           <t>narrateur|Zoé a pris quoi, près des fleurs ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6861,6 +6898,7 @@
           <t>narrateur|Les fleurs sentent bon. Zoé aussi respire. Le mouchoir est à la poubelle.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7060,6 +7098,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7227,6 +7266,7 @@
           <t>narrateur|Léa empile des cubes. Zoé a le nez propre. Mouchoir, poubelle. Elle pose un cube bleu.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7422,6 +7462,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7589,6 +7630,7 @@
           <t>narrateur|Une pomme dans le sac. Zoé a jeté le mouchoir à la poubelle. Léa applaudit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7756,6 +7798,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7923,6 +7966,7 @@
           <t>narrateur|Un yaourt. Zoé a pris un mouchoir. Poubelle. Léa tient la main.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8090,6 +8134,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8258,6 +8303,7 @@
 enfant-f|On y va.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8425,6 +8471,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8592,6 +8639,7 @@
           <t>narrateur|Léa ouvre un livre d'images. Zoé a déjà mis le mouchoir à la poubelle. Elle écoute. Papa tourne la page.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8787,6 +8835,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8954,6 +9003,7 @@
           <t>narrateur|Papa prend une pomme. Zoé a le mouchoir à la poubelle. Léa ferme le livre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9121,6 +9171,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9288,6 +9339,7 @@
           <t>narrateur|Maman prend un yaourt. Zoé a pris un mouchoir. Puis la poubelle.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9455,6 +9507,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9622,6 +9675,7 @@
           <t>narrateur|Le pain est dans le filet. Zoé a jeté le mouchoir. Poubelle.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9789,6 +9843,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9957,6 +10012,7 @@
 narrateur|À table.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10152,6 +10208,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10319,6 +10376,7 @@
           <t>narrateur|Une vraie pomme. Zoé a mis le mouchoir à la poubelle. Léa range.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10486,6 +10544,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10653,6 +10712,7 @@
           <t>narrateur|Un vrai yaourt. Zoé a pris un mouchoir. Poubelle.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10820,6 +10880,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10987,6 +11048,7 @@
           <t>narrateur|Un vrai morceau de pain. Zoé a le mouchoir à la poubelle. Léa dit merci.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11154,6 +11216,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11323,6 +11386,7 @@
 narrateur|Zoé prend un mouchoir. Elle se mouche. Sami montre la poubelle. Zoé jette. Son nez est plus libre.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11510,6 +11574,7 @@
           <t>narrateur|Sami montre la poubelle. Zoé a pris quoi avant ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11681,6 +11746,7 @@
           <t>narrateur|Le pain sent bon. Zoé respire mieux. Le mouchoir est à la poubelle.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11880,6 +11946,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12047,6 +12114,7 @@
           <t>narrateur|Sami construit. Zoé a déjà jeté le mouchoir à la poubelle. Elle pose un cube. Papa surveille.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12242,6 +12310,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12409,6 +12478,7 @@
           <t>narrateur|Une pomme pour plus tard. Zoé a le mouchoir à la poubelle. Sami range les cubes.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12576,6 +12646,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12744,6 +12815,7 @@
 enfant-m|On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12911,6 +12983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13078,6 +13151,7 @@
           <t>narrateur|Le pain de Sami. Zoé a jeté le mouchoir à la poubelle.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13245,6 +13319,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13413,6 +13488,7 @@
 maman|Bien.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13608,6 +13684,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13775,6 +13852,7 @@
           <t>narrateur|Papa choisit une pomme. Zoé a le mouchoir à la poubelle. Sami ferme le livre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13942,6 +14020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14109,6 +14188,7 @@
           <t>narrateur|Maman choisit un yaourt. Zoé a pris un mouchoir. Poubelle.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14276,6 +14356,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14443,6 +14524,7 @@
           <t>narrateur|Sami sent le pain. Zoé a jeté le mouchoir. Poubelle.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14610,6 +14692,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14777,6 +14860,7 @@
           <t>narrateur|Sami fait la dînette. Zoé a le nez libre. Le mouchoir est déjà à la poubelle. Elle sert une tasse imaginaire.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14972,6 +15056,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15139,6 +15224,7 @@
           <t>narrateur|Une pomme vraie. Zoé a mis le mouchoir à la poubelle. Sami range.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15306,6 +15392,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15473,6 +15560,7 @@
           <t>narrateur|Un yaourt vrai. Zoé a pris un mouchoir. Puis la poubelle.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15640,6 +15728,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15808,6 +15897,7 @@
 enfant-m|Au revoir marché.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15975,6 +16065,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15993,7 +16084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16038,6 +16129,20 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16239,6 +16344,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
